--- a/data/trans_dic/P64D$publico_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,95; 28,09</t>
+          <t>5,85; 28,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 34,18</t>
+          <t>11,92; 34,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 25,82</t>
+          <t>10,8; 26,18</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 10,35</t>
+          <t>3,8; 10,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,82</t>
+          <t>3,46; 10,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,56</t>
+          <t>4,71; 9,51</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 10,61</t>
+          <t>5,47; 10,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,15</t>
+          <t>6,21; 11,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,93</t>
+          <t>6,32; 9,8</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,6</t>
+          <t>1,31; 6,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,23</t>
+          <t>8,3; 15,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,08</t>
+          <t>3,14; 9,03</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,48; 13,09</t>
+          <t>6,42; 12,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,66</t>
+          <t>8,27; 15,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 12,31</t>
+          <t>7,94; 12,46</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 27,42</t>
+          <t>2,99; 26,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 15,25</t>
+          <t>1,7; 14,42</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,06</t>
+          <t>4,11; 8,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,15</t>
+          <t>8,21; 11,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,33</t>
+          <t>6,33; 9,28</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en transporte público (autobús, metro, tren) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5392; 25453</t>
+          <t>5302; 25881</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9202; 27766</t>
+          <t>9682; 28186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18494; 44380</t>
+          <t>18555; 44993</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13686; 36246</t>
+          <t>13310; 36062</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11291; 37844</t>
+          <t>12116; 37413</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32105; 66948</t>
+          <t>32978; 66552</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24917; 48994</t>
+          <t>25267; 49773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21160; 39169</t>
+          <t>21800; 39680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51923; 80768</t>
+          <t>51387; 79660</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11037; 49189</t>
+          <t>9754; 46365</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38019; 68962</t>
+          <t>37569; 71633</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42453; 108757</t>
+          <t>37617; 108163</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19398; 39146</t>
+          <t>19193; 38322</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16973; 30520</t>
+          <t>17209; 31475</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40020; 62459</t>
+          <t>40282; 63216</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 946</t>
+          <t>0; 919</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>572; 4868</t>
+          <t>532; 4644</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>728; 5292</t>
+          <t>591; 5003</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>83786; 158391</t>
+          <t>80741; 158237</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>122483; 177543</t>
+          <t>119889; 174491</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>213515; 319655</t>
+          <t>217072; 317880</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$publico_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$publico_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 28,56</t>
+          <t>7,08; 27,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,92; 34,7</t>
+          <t>11,17; 33,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 26,18</t>
+          <t>11,57; 27,07</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 10,29</t>
+          <t>5,16; 12,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 10,7</t>
+          <t>7,27; 14,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,51</t>
+          <t>7,12; 12,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,77</t>
+          <t>5,73; 10,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,3</t>
+          <t>6,61; 11,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 9,8</t>
+          <t>6,81; 10,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,22</t>
+          <t>4,32; 8,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 15,82</t>
+          <t>9,53; 14,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,03</t>
+          <t>7,32; 10,61</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 12,81</t>
+          <t>6,93; 13,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 15,12</t>
+          <t>8,69; 15,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 12,46</t>
+          <t>8,45; 13,09</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 19,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 26,16</t>
+          <t>3,03; 27,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,42</t>
+          <t>3,01; 18,3</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,05</t>
+          <t>6,88; 9,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,94</t>
+          <t>9,91; 12,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,28</t>
+          <t>8,57; 10,66</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17357</t>
+          <t>19512</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30388</t>
+          <t>35558</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5302; 25881</t>
+          <t>7420; 29318</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9682; 28186</t>
+          <t>10250; 30601</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18555; 44993</t>
+          <t>22739; 53218</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>32478</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48669</t>
+          <t>66155</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13310; 36062</t>
+          <t>20419; 49304</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12116; 37413</t>
+          <t>22912; 46613</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32978; 66552</t>
+          <t>50594; 86153</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36063</t>
+          <t>43602</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65212</t>
+          <t>78133</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25267; 49773</t>
+          <t>30728; 57580</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21800; 39680</t>
+          <t>26243; 45814</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51387; 79660</t>
+          <t>63538; 96356</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>33650</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>54986</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79484</t>
+          <t>88636</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9754; 46365</t>
+          <t>23505; 47183</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37569; 71633</t>
+          <t>43338; 66997</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37617; 108163</t>
+          <t>73099; 105932</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27310</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>27752</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50595</t>
+          <t>59719</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19193; 38322</t>
+          <t>22677; 43490</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17209; 31475</t>
+          <t>20227; 36472</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40282; 63216</t>
+          <t>47352; 73332</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>816</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>3133</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 919</t>
+          <t>0; 3737</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>532; 4644</t>
+          <t>598; 5495</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>591; 5003</t>
+          <t>1169; 7115</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>158560</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>148643</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>276625</t>
+          <t>331335</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>80741; 158237</t>
+          <t>132684; 189371</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>119889; 174491</t>
+          <t>149700; 195560</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>217072; 317880</t>
+          <t>294712; 366744</t>
         </is>
       </c>
     </row>
